--- a/download/Domaine1_Recrutement_Candidats_KPIs.xlsx
+++ b/download/Domaine1_Recrutement_Candidats_KPIs.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -211,6 +211,36 @@
       <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="00D4820A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="008C8A84"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="0037352F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -305,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -482,11 +512,43 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="19">
     <dxf>
       <font>
         <color rgb="00D4820A"/>
@@ -643,6 +705,45 @@
         <name val="Noto Sans CJK SC"/>
         <color rgb="00C0392B"/>
         <sz val="14"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FDEDEC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Noto Sans CJK SC"/>
+        <b val="1"/>
+        <color rgb="001B7D46"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Noto Sans CJK SC"/>
+        <b val="1"/>
+        <color rgb="00D4820A"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FEF9E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Noto Sans CJK SC"/>
+        <b val="1"/>
+        <color rgb="00C0392B"/>
+        <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -894,56 +995,6 @@
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>System</author>
-  </authors>
-  <commentList>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>Delai moyen entre demande et pourvoiement</t>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>Cout moyen par recrutement</t>
-      </text>
-    </comment>
-    <comment ref="B9" authorId="0" shapeId="0">
-      <text>
-        <t>Score moyen evaluation candidats retenus</t>
-      </text>
-    </comment>
-    <comment ref="B10" authorId="0" shapeId="0">
-      <text>
-        <t>Offres acceptees / Offres envoyees</t>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0">
-      <text>
-        <t>Postes pourvus / Total demandes</t>
-      </text>
-    </comment>
-    <comment ref="B12" authorId="0" shapeId="0">
-      <text>
-        <t>Candidats recommandes / Total evalues</t>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
-      <text>
-        <t>Volume de candidatures par recrutement</t>
-      </text>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0">
-      <text>
-        <t>Efficacite du processus de selection</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -29298,28 +29349,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:R45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -29330,7 +29382,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Suivi des indicateurs cles de performance — Donnees automatiques</t>
@@ -29355,6 +29407,7 @@
       <c r="L5" s="61" t="n"/>
       <c r="M5" s="61" t="n"/>
       <c r="N5" s="61" t="n"/>
+      <c r="O5" s="61" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="B6" s="5" t="inlineStr">
@@ -29429,579 +29482,475 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="62" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>Time-to-Hire (jours)</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=1)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=1)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="D7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=2)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=2)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="E7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=3)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=3)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="F7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=4)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=4)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="G7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=5)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=5)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="H7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=6)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=6)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="I7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=7)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=7)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="J7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=8)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=8)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="K7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=9)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=9)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="L7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=10)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=10)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="M7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=11)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=11)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="N7" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=12)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=12)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="O7" s="64" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(C7:N7),0)</t>
-        </is>
+      <c r="C7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=1)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=1)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=2)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=2)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=3)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=3)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=4)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=4)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=5)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=5)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=6)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=6)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=7)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=7)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="J7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=8)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=8)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=9)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=9)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=10)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=10)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="M7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=11)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=11)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="N7" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=12)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")*('1-Demandes Recrutement'!$M$5:$M$85-'1-Demandes Recrutement'!$C$5:$C$85))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$M$5:$M$85)=12)*('1-Demandes Recrutement'!$M$5:$M$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="O7" s="64">
+        <f>IFERROR(AVERAGE(C7:N7),0)</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>Cost-per-Hire (FCFA)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=1)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=1)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=2)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=2)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=3)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=3)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=4)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=4)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=5)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=5)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=6)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=6)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=7)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=7)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=8)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=8)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=9)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=9)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=10)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=10)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=11)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=11)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=12)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=12)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="O8" s="65" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(C8:N8),0)</t>
-        </is>
+      <c r="C8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=1)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=1)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=2)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=2)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=3)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=3)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=4)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=4)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=5)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=5)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=6)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=6)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="I8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=7)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=7)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=8)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=8)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=9)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=9)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=10)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=10)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=11)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=11)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="N8" s="82">
+        <f>IFERROR(SUMPRODUCT((MONTH('10-Analyse Couts'!$K$5:$K$85)=12)*('10-Analyse Couts'!$F$5:$F$85+'10-Analyse Couts'!$G$5:$G$85+'10-Analyse Couts'!$H$5:$H$85+'10-Analyse Couts'!$I$5:$I$85))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=12)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="O8" s="65">
+        <f>IFERROR(AVERAGE(C8:N8),0)</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="62" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>Quality-of-Hire (/20)</t>
         </is>
       </c>
-      <c r="C9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=1)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=1)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="D9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=2)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=2)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="E9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=3)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=3)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="F9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=4)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=4)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="G9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=5)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=5)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="H9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=6)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=6)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="I9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=7)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=7)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="J9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=8)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=8)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="K9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=9)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=9)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="L9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=10)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=10)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="M9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=11)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=11)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="N9" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=12)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=12)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="O9" s="64" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(C9:N9),0)</t>
-        </is>
+      <c r="C9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=1)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=1)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=2)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=2)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=3)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=3)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=4)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=4)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=5)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=5)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=6)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=6)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="I9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=7)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=7)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="J9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=8)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=8)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=9)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=9)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=10)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=10)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=11)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=11)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="N9" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=12)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=12)*('4-Grille Evaluation'!$L$5:$L$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="O9" s="64">
+        <f>IFERROR(AVERAGE(C9:N9),0)</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>Taux acceptation offres (%)</t>
         </is>
       </c>
-      <c r="C10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=1)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=1)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=1)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="D10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=2)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=2)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=2)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="E10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=3)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=3)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=3)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="F10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=4)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=4)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=4)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="G10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=5)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=5)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=5)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="H10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=6)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=6)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=6)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="I10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=7)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=7)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=7)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="J10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=8)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=8)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=8)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="K10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=9)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=9)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=9)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="L10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=10)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=10)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=10)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="M10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=11)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=11)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=11)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="N10" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=12)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=12)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=12)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</t>
-        </is>
-      </c>
-      <c r="O10" s="67" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(C10:N10),0)</t>
-        </is>
+      <c r="C10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=1)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=1)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=1)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=2)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=2)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=2)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="E10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=3)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=3)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=3)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=4)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=4)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=4)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=5)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=5)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=5)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=6)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=6)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=6)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="I10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=7)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=7)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=7)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=8)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=8)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=8)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=9)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=9)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=9)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=10)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=10)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=10)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="M10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=11)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=11)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=11)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="N10" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=12)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))/MAX(SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=12)*('18-Pipeline Candidatures'!$H$5:$H$85="Accepte"))+SUMPRODUCT((MONTH('18-Pipeline Candidatures'!$G$5:$G$85)=12)*('18-Pipeline Candidatures'!$H$5:$H$85="Refuse")),1),0)</f>
+        <v/>
+      </c>
+      <c r="O10" s="67">
+        <f>IFERROR(AVERAGE(C10:N10),0)</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="62" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>Taux de remplissage (%)</t>
         </is>
       </c>
-      <c r="C11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=1)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=1)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="D11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=2)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=2)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="E11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=3)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=3)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="F11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=4)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=4)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="G11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=5)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=5)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="H11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=6)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=6)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="I11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=7)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=7)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="J11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=8)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=8)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="K11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=9)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=9)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="L11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=10)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=10)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="M11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=11)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=11)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="N11" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=12)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=12)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="O11" s="67" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(C11:N11),0)</t>
-        </is>
+      <c r="C11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=1)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=1)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=2)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=2)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=3)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=3)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=4)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=4)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=5)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=5)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=6)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=6)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="I11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=7)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=7)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="J11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=8)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=8)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=9)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=9)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="L11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=10)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=10)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="M11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=11)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=11)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="N11" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=12)*('1-Demandes Recrutement'!$L$5:$L$85="Pourvue"))/MAX(SUMPRODUCT((MONTH('1-Demandes Recrutement'!$C$5:$C$85)=12)*('1-Demandes Recrutement'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="O11" s="67">
+        <f>IFERROR(AVERAGE(C11:N11),0)</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>Taux de recommandation (%)</t>
         </is>
       </c>
-      <c r="C12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=1)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=1)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="D12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=2)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=2)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="E12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=3)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=3)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="F12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=4)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=4)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="G12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=5)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=5)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="H12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=6)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=6)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="I12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=7)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=7)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="J12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=8)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=8)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="K12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=9)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=9)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="L12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=10)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=10)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="M12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=11)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=11)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="N12" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=12)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=12)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="O12" s="67" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(C12:N12),0)</t>
-        </is>
+      <c r="C12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=1)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=1)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=2)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=2)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="E12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=3)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=3)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=4)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=4)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=5)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=5)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=6)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=6)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="I12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=7)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=7)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="J12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=8)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=8)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=9)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=9)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="L12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=10)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=10)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="M12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=11)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=11)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="N12" s="83">
+        <f>IFERROR(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=12)*('4-Grille Evaluation'!$M$5:$M$85="Embauche recommandee"))/MAX(SUMPRODUCT((MONTH('4-Grille Evaluation'!$E$5:$E$85)=12)*('4-Grille Evaluation'!$B$5:$B$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="O12" s="67">
+        <f>IFERROR(AVERAGE(C12:N12),0)</f>
+        <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="62" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>Nb candidats / embauche</t>
         </is>
       </c>
-      <c r="C13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=1)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=1)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="D13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=2)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=2)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="E13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=3)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=3)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="F13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=4)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=4)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="G13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=5)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=5)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="H13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=6)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=6)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="I13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=7)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=7)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="J13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=8)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=8)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="K13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=9)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=9)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="L13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=10)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=10)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="M13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=11)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=11)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="N13" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=12)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=12)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="O13" s="64" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(C13:N13),0)</t>
-        </is>
+      <c r="C13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=1)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=1)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=2)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=2)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="E13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=3)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=3)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=4)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=4)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=5)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=5)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=6)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=6)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="I13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=7)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=7)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=8)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=8)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=9)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=9)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="L13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=10)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=10)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=11)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=11)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="N13" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('2-Base Candidats'!$Y$5:$Y$85)=12)*('2-Base Candidats'!$B$5:$B$85&lt;&gt;""))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=12)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="O13" s="64">
+        <f>IFERROR(AVERAGE(C13:N13),0)</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>Entretiens / embauche</t>
         </is>
       </c>
-      <c r="C14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=1)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=1)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="D14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=2)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=2)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="E14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=3)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=3)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="F14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=4)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=4)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="G14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=5)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=5)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="H14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=6)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=6)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="I14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=7)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=7)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="J14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=8)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=8)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="K14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=9)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=9)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="L14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=10)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=10)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="M14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=11)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=11)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="N14" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=12)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=12)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</t>
-        </is>
-      </c>
-      <c r="O14" s="64" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(C14:N14),0)</t>
-        </is>
+      <c r="C14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=1)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=1)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=2)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=2)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=3)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=3)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=4)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=4)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=5)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=5)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=6)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=6)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=7)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=7)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=8)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=8)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=9)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=9)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=10)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=10)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=11)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=11)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="N14" s="81">
+        <f>IFERROR(SUMPRODUCT((MONTH('3-Planning Entretiens'!$E$5:$E$85)=12)*('3-Planning Entretiens'!$K$5:$K$85="Realise"))/MAX(SUMPRODUCT((MONTH('2-Base Candidats'!$AF$5:$AF$85)=12)*('2-Base Candidats'!$AF$5:$AF$85&lt;&gt;"")),1),0)</f>
+        <v/>
+      </c>
+      <c r="O14" s="64">
+        <f>IFERROR(AVERAGE(C14:N14),0)</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
@@ -30150,606 +30099,542 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="62" t="inlineStr">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>Time-to-Hire (jours)</t>
         </is>
       </c>
-      <c r="C20" s="71" t="n">
+      <c r="C20" s="84" t="n">
         <v>45</v>
       </c>
-      <c r="D20" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!C7,19-KPIs &amp; Objectifs RH!D7,19-KPIs &amp; Objectifs RH!E7),0)</t>
-        </is>
-      </c>
-      <c r="E20" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((C20-D20)/MAX(ABS(C20),0.001),0)</t>
-        </is>
-      </c>
-      <c r="F20" s="73">
-        <f>IF(E20&gt;=0.1,"✅",IF(E20&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="G20" s="71" t="n">
+      <c r="D20" s="81">
+        <f>IFERROR(AVERAGE(C7,D7,E7),0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="85">
+        <f>IFERROR((C20-D20)/MAX(ABS(C20),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="86">
+        <f>IF(E20&gt;=0.1,"OK",IF(E20&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="84" t="n">
         <v>35</v>
       </c>
-      <c r="H20" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!F7,19-KPIs &amp; Objectifs RH!G7,19-KPIs &amp; Objectifs RH!H7),0)</t>
-        </is>
-      </c>
-      <c r="I20" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((G20-H20)/MAX(ABS(G20),0.001),0)</t>
-        </is>
-      </c>
-      <c r="J20" s="73">
-        <f>IF(I20&gt;=0.1,"✅",IF(I20&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="K20" s="71" t="n">
+      <c r="H20" s="81">
+        <f>IFERROR(AVERAGE(F7,G7,H7),0)</f>
+        <v/>
+      </c>
+      <c r="I20" s="85">
+        <f>IFERROR((G20-H20)/MAX(ABS(G20),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="86">
+        <f>IF(I20&gt;=0.1,"OK",IF(I20&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="K20" s="84" t="n">
         <v>30</v>
       </c>
-      <c r="L20" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!I7,19-KPIs &amp; Objectifs RH!J7,19-KPIs &amp; Objectifs RH!K7),0)</t>
-        </is>
-      </c>
-      <c r="M20" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((K20-L20)/MAX(ABS(K20),0.001),0)</t>
-        </is>
-      </c>
-      <c r="N20" s="73">
-        <f>IF(M20&gt;=0.1,"✅",IF(M20&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="O20" s="71" t="n">
+      <c r="L20" s="81">
+        <f>IFERROR(AVERAGE(I7,J7,K7),0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="85">
+        <f>IFERROR((K20-L20)/MAX(ABS(K20),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="N20" s="86">
+        <f>IF(M20&gt;=0.1,"OK",IF(M20&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="O20" s="84" t="n">
         <v>30</v>
       </c>
-      <c r="P20" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!L7,19-KPIs &amp; Objectifs RH!M7,19-KPIs &amp; Objectifs RH!N7),0)</t>
-        </is>
-      </c>
-      <c r="Q20" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((O20-P20)/MAX(ABS(O20),0.001),0)</t>
-        </is>
-      </c>
-      <c r="R20" s="73">
-        <f>IF(Q20&gt;=0.1,"✅",IF(Q20&gt;=-0.1,"⚠️","❌"))</f>
+      <c r="P20" s="81">
+        <f>IFERROR(AVERAGE(L7,M7,N7),0)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="85">
+        <f>IFERROR((O20-P20)/MAX(ABS(O20),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="R20" s="86">
+        <f>IF(Q20&gt;=0.1,"OK",IF(Q20&gt;=-0.1,"ATT","NOK"))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="62" t="inlineStr">
+      <c r="B21" s="80" t="inlineStr">
         <is>
           <t>Cost-per-Hire (FCFA)</t>
         </is>
       </c>
-      <c r="C21" s="74" t="n">
+      <c r="C21" s="87" t="n">
         <v>200000</v>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!C8,19-KPIs &amp; Objectifs RH!D8,19-KPIs &amp; Objectifs RH!E8),0)</t>
-        </is>
-      </c>
-      <c r="E21" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((C21-D21)/MAX(ABS(C21),0.001),0)</t>
-        </is>
-      </c>
-      <c r="F21" s="73">
-        <f>IF(E21&gt;=0.1,"✅",IF(E21&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="G21" s="74" t="n">
+      <c r="D21" s="82">
+        <f>IFERROR(AVERAGE(C8,D8,E8),0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="85">
+        <f>IFERROR((C21-D21)/MAX(ABS(C21),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="86">
+        <f>IF(E21&gt;=0.1,"OK",IF(E21&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="G21" s="87" t="n">
         <v>180000</v>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!F8,19-KPIs &amp; Objectifs RH!G8,19-KPIs &amp; Objectifs RH!H8),0)</t>
-        </is>
-      </c>
-      <c r="I21" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((G21-H21)/MAX(ABS(G21),0.001),0)</t>
-        </is>
-      </c>
-      <c r="J21" s="73">
-        <f>IF(I21&gt;=0.1,"✅",IF(I21&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="K21" s="74" t="n">
+      <c r="H21" s="82">
+        <f>IFERROR(AVERAGE(F8,G8,H8),0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="85">
+        <f>IFERROR((G21-H21)/MAX(ABS(G21),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="86">
+        <f>IF(I21&gt;=0.1,"OK",IF(I21&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="K21" s="87" t="n">
         <v>150000</v>
       </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!I8,19-KPIs &amp; Objectifs RH!J8,19-KPIs &amp; Objectifs RH!K8),0)</t>
-        </is>
-      </c>
-      <c r="M21" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((K21-L21)/MAX(ABS(K21),0.001),0)</t>
-        </is>
-      </c>
-      <c r="N21" s="73">
-        <f>IF(M21&gt;=0.1,"✅",IF(M21&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="O21" s="74" t="n">
+      <c r="L21" s="82">
+        <f>IFERROR(AVERAGE(I8,J8,K8),0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="85">
+        <f>IFERROR((K21-L21)/MAX(ABS(K21),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="86">
+        <f>IF(M21&gt;=0.1,"OK",IF(M21&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="O21" s="87" t="n">
         <v>150000</v>
       </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!L8,19-KPIs &amp; Objectifs RH!M8,19-KPIs &amp; Objectifs RH!N8),0)</t>
-        </is>
-      </c>
-      <c r="Q21" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((O21-P21)/MAX(ABS(O21),0.001),0)</t>
-        </is>
-      </c>
-      <c r="R21" s="73">
-        <f>IF(Q21&gt;=0.1,"✅",IF(Q21&gt;=-0.1,"⚠️","❌"))</f>
+      <c r="P21" s="82">
+        <f>IFERROR(AVERAGE(L8,M8,N8),0)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="85">
+        <f>IFERROR((O21-P21)/MAX(ABS(O21),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="86">
+        <f>IF(Q21&gt;=0.1,"OK",IF(Q21&gt;=-0.1,"ATT","NOK"))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="62" t="inlineStr">
+      <c r="B22" s="80" t="inlineStr">
         <is>
           <t>Quality-of-Hire (/20)</t>
         </is>
       </c>
-      <c r="C22" s="71" t="n">
+      <c r="C22" s="84" t="n">
         <v>13</v>
       </c>
-      <c r="D22" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!C9,19-KPIs &amp; Objectifs RH!D9,19-KPIs &amp; Objectifs RH!E9),0)</t>
-        </is>
-      </c>
-      <c r="E22" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((D22-C22)/MAX(ABS(C22),0.001),0)</t>
-        </is>
-      </c>
-      <c r="F22" s="73">
-        <f>IF(E22&gt;=0.1,"✅",IF(E22&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="71" t="n">
+      <c r="D22" s="81">
+        <f>IFERROR(AVERAGE(C9,D9,E9),0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="85">
+        <f>IFERROR((D22-C22)/MAX(ABS(C22),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="86">
+        <f>IF(E22&gt;=0.1,"OK",IF(E22&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="84" t="n">
         <v>14</v>
       </c>
-      <c r="H22" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!F9,19-KPIs &amp; Objectifs RH!G9,19-KPIs &amp; Objectifs RH!H9),0)</t>
-        </is>
-      </c>
-      <c r="I22" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((H22-G22)/MAX(ABS(G22),0.001),0)</t>
-        </is>
-      </c>
-      <c r="J22" s="73">
-        <f>IF(I22&gt;=0.1,"✅",IF(I22&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="K22" s="71" t="n">
+      <c r="H22" s="81">
+        <f>IFERROR(AVERAGE(F9,G9,H9),0)</f>
+        <v/>
+      </c>
+      <c r="I22" s="85">
+        <f>IFERROR((H22-G22)/MAX(ABS(G22),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="86">
+        <f>IF(I22&gt;=0.1,"OK",IF(I22&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="K22" s="84" t="n">
         <v>15</v>
       </c>
-      <c r="L22" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!I9,19-KPIs &amp; Objectifs RH!J9,19-KPIs &amp; Objectifs RH!K9),0)</t>
-        </is>
-      </c>
-      <c r="M22" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((L22-K22)/MAX(ABS(K22),0.001),0)</t>
-        </is>
-      </c>
-      <c r="N22" s="73">
-        <f>IF(M22&gt;=0.1,"✅",IF(M22&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="O22" s="71" t="n">
+      <c r="L22" s="81">
+        <f>IFERROR(AVERAGE(I9,J9,K9),0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="85">
+        <f>IFERROR((L22-K22)/MAX(ABS(K22),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="86">
+        <f>IF(M22&gt;=0.1,"OK",IF(M22&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="O22" s="84" t="n">
         <v>16</v>
       </c>
-      <c r="P22" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!L9,19-KPIs &amp; Objectifs RH!M9,19-KPIs &amp; Objectifs RH!N9),0)</t>
-        </is>
-      </c>
-      <c r="Q22" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((P22-O22)/MAX(ABS(O22),0.001),0)</t>
-        </is>
-      </c>
-      <c r="R22" s="73">
-        <f>IF(Q22&gt;=0.1,"✅",IF(Q22&gt;=-0.1,"⚠️","❌"))</f>
+      <c r="P22" s="81">
+        <f>IFERROR(AVERAGE(L9,M9,N9),0)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="85">
+        <f>IFERROR((P22-O22)/MAX(ABS(O22),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="R22" s="86">
+        <f>IF(Q22&gt;=0.1,"OK",IF(Q22&gt;=-0.1,"ATT","NOK"))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="62" t="inlineStr">
+      <c r="B23" s="80" t="inlineStr">
         <is>
           <t>Taux acceptation offres (%)</t>
         </is>
       </c>
-      <c r="C23" s="75" t="n">
+      <c r="C23" s="88" t="n">
         <v>0.6</v>
       </c>
-      <c r="D23" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!C10,19-KPIs &amp; Objectifs RH!D10,19-KPIs &amp; Objectifs RH!E10),0)</t>
-        </is>
-      </c>
-      <c r="E23" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((D23-C23)/MAX(ABS(C23),0.001),0)</t>
-        </is>
-      </c>
-      <c r="F23" s="73">
-        <f>IF(E23&gt;=0.1,"✅",IF(E23&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="G23" s="75" t="n">
+      <c r="D23" s="83">
+        <f>IFERROR(AVERAGE(C10,D10,E10),0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="85">
+        <f>IFERROR((D23-C23)/MAX(ABS(C23),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="86">
+        <f>IF(E23&gt;=0.1,"OK",IF(E23&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="88" t="n">
         <v>0.7</v>
       </c>
-      <c r="H23" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!F10,19-KPIs &amp; Objectifs RH!G10,19-KPIs &amp; Objectifs RH!H10),0)</t>
-        </is>
-      </c>
-      <c r="I23" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((H23-G23)/MAX(ABS(G23),0.001),0)</t>
-        </is>
-      </c>
-      <c r="J23" s="73">
-        <f>IF(I23&gt;=0.1,"✅",IF(I23&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="K23" s="75" t="n">
+      <c r="H23" s="83">
+        <f>IFERROR(AVERAGE(F10,G10,H10),0)</f>
+        <v/>
+      </c>
+      <c r="I23" s="85">
+        <f>IFERROR((H23-G23)/MAX(ABS(G23),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="86">
+        <f>IF(I23&gt;=0.1,"OK",IF(I23&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="K23" s="88" t="n">
         <v>0.75</v>
       </c>
-      <c r="L23" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!I10,19-KPIs &amp; Objectifs RH!J10,19-KPIs &amp; Objectifs RH!K10),0)</t>
-        </is>
-      </c>
-      <c r="M23" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((L23-K23)/MAX(ABS(K23),0.001),0)</t>
-        </is>
-      </c>
-      <c r="N23" s="73">
-        <f>IF(M23&gt;=0.1,"✅",IF(M23&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="O23" s="75" t="n">
+      <c r="L23" s="83">
+        <f>IFERROR(AVERAGE(I10,J10,K10),0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="85">
+        <f>IFERROR((L23-K23)/MAX(ABS(K23),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="N23" s="86">
+        <f>IF(M23&gt;=0.1,"OK",IF(M23&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="O23" s="88" t="n">
         <v>0.8</v>
       </c>
-      <c r="P23" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!L10,19-KPIs &amp; Objectifs RH!M10,19-KPIs &amp; Objectifs RH!N10),0)</t>
-        </is>
-      </c>
-      <c r="Q23" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((P23-O23)/MAX(ABS(O23),0.001),0)</t>
-        </is>
-      </c>
-      <c r="R23" s="73">
-        <f>IF(Q23&gt;=0.1,"✅",IF(Q23&gt;=-0.1,"⚠️","❌"))</f>
+      <c r="P23" s="83">
+        <f>IFERROR(AVERAGE(L10,M10,N10),0)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="85">
+        <f>IFERROR((P23-O23)/MAX(ABS(O23),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="R23" s="86">
+        <f>IF(Q23&gt;=0.1,"OK",IF(Q23&gt;=-0.1,"ATT","NOK"))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="62" t="inlineStr">
+      <c r="B24" s="80" t="inlineStr">
         <is>
           <t>Taux de remplissage (%)</t>
         </is>
       </c>
-      <c r="C24" s="75" t="n">
+      <c r="C24" s="88" t="n">
         <v>0.5</v>
       </c>
-      <c r="D24" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!C11,19-KPIs &amp; Objectifs RH!D11,19-KPIs &amp; Objectifs RH!E11),0)</t>
-        </is>
-      </c>
-      <c r="E24" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((D24-C24)/MAX(ABS(C24),0.001),0)</t>
-        </is>
-      </c>
-      <c r="F24" s="73">
-        <f>IF(E24&gt;=0.1,"✅",IF(E24&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="G24" s="75" t="n">
+      <c r="D24" s="83">
+        <f>IFERROR(AVERAGE(C11,D11,E11),0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="85">
+        <f>IFERROR((D24-C24)/MAX(ABS(C24),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="86">
+        <f>IF(E24&gt;=0.1,"OK",IF(E24&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="88" t="n">
         <v>0.6</v>
       </c>
-      <c r="H24" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!F11,19-KPIs &amp; Objectifs RH!G11,19-KPIs &amp; Objectifs RH!H11),0)</t>
-        </is>
-      </c>
-      <c r="I24" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((H24-G24)/MAX(ABS(G24),0.001),0)</t>
-        </is>
-      </c>
-      <c r="J24" s="73">
-        <f>IF(I24&gt;=0.1,"✅",IF(I24&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="K24" s="75" t="n">
+      <c r="H24" s="83">
+        <f>IFERROR(AVERAGE(F11,G11,H11),0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="85">
+        <f>IFERROR((H24-G24)/MAX(ABS(G24),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="86">
+        <f>IF(I24&gt;=0.1,"OK",IF(I24&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="K24" s="88" t="n">
         <v>0.7</v>
       </c>
-      <c r="L24" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!I11,19-KPIs &amp; Objectifs RH!J11,19-KPIs &amp; Objectifs RH!K11),0)</t>
-        </is>
-      </c>
-      <c r="M24" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((L24-K24)/MAX(ABS(K24),0.001),0)</t>
-        </is>
-      </c>
-      <c r="N24" s="73">
-        <f>IF(M24&gt;=0.1,"✅",IF(M24&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="O24" s="75" t="n">
+      <c r="L24" s="83">
+        <f>IFERROR(AVERAGE(I11,J11,K11),0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="85">
+        <f>IFERROR((L24-K24)/MAX(ABS(K24),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="N24" s="86">
+        <f>IF(M24&gt;=0.1,"OK",IF(M24&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="O24" s="88" t="n">
         <v>0.75</v>
       </c>
-      <c r="P24" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!L11,19-KPIs &amp; Objectifs RH!M11,19-KPIs &amp; Objectifs RH!N11),0)</t>
-        </is>
-      </c>
-      <c r="Q24" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((P24-O24)/MAX(ABS(O24),0.001),0)</t>
-        </is>
-      </c>
-      <c r="R24" s="73">
-        <f>IF(Q24&gt;=0.1,"✅",IF(Q24&gt;=-0.1,"⚠️","❌"))</f>
+      <c r="P24" s="83">
+        <f>IFERROR(AVERAGE(L11,M11,N11),0)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="85">
+        <f>IFERROR((P24-O24)/MAX(ABS(O24),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="R24" s="86">
+        <f>IF(Q24&gt;=0.1,"OK",IF(Q24&gt;=-0.1,"ATT","NOK"))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="62" t="inlineStr">
+      <c r="B25" s="80" t="inlineStr">
         <is>
           <t>Taux de recommandation (%)</t>
         </is>
       </c>
-      <c r="C25" s="75" t="n">
+      <c r="C25" s="88" t="n">
         <v>0.4</v>
       </c>
-      <c r="D25" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!C12,19-KPIs &amp; Objectifs RH!D12,19-KPIs &amp; Objectifs RH!E12),0)</t>
-        </is>
-      </c>
-      <c r="E25" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((D25-C25)/MAX(ABS(C25),0.001),0)</t>
-        </is>
-      </c>
-      <c r="F25" s="73">
-        <f>IF(E25&gt;=0.1,"✅",IF(E25&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="G25" s="75" t="n">
+      <c r="D25" s="83">
+        <f>IFERROR(AVERAGE(C12,D12,E12),0)</f>
+        <v/>
+      </c>
+      <c r="E25" s="85">
+        <f>IFERROR((D25-C25)/MAX(ABS(C25),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="86">
+        <f>IF(E25&gt;=0.1,"OK",IF(E25&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="88" t="n">
         <v>0.5</v>
       </c>
-      <c r="H25" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!F12,19-KPIs &amp; Objectifs RH!G12,19-KPIs &amp; Objectifs RH!H12),0)</t>
-        </is>
-      </c>
-      <c r="I25" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((H25-G25)/MAX(ABS(G25),0.001),0)</t>
-        </is>
-      </c>
-      <c r="J25" s="73">
-        <f>IF(I25&gt;=0.1,"✅",IF(I25&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="K25" s="75" t="n">
+      <c r="H25" s="83">
+        <f>IFERROR(AVERAGE(F12,G12,H12),0)</f>
+        <v/>
+      </c>
+      <c r="I25" s="85">
+        <f>IFERROR((H25-G25)/MAX(ABS(G25),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="J25" s="86">
+        <f>IF(I25&gt;=0.1,"OK",IF(I25&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="K25" s="88" t="n">
         <v>0.55</v>
       </c>
-      <c r="L25" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!I12,19-KPIs &amp; Objectifs RH!J12,19-KPIs &amp; Objectifs RH!K12),0)</t>
-        </is>
-      </c>
-      <c r="M25" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((L25-K25)/MAX(ABS(K25),0.001),0)</t>
-        </is>
-      </c>
-      <c r="N25" s="73">
-        <f>IF(M25&gt;=0.1,"✅",IF(M25&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="O25" s="75" t="n">
+      <c r="L25" s="83">
+        <f>IFERROR(AVERAGE(I12,J12,K12),0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="85">
+        <f>IFERROR((L25-K25)/MAX(ABS(K25),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="N25" s="86">
+        <f>IF(M25&gt;=0.1,"OK",IF(M25&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="O25" s="88" t="n">
         <v>0.6</v>
       </c>
-      <c r="P25" s="66" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!L12,19-KPIs &amp; Objectifs RH!M12,19-KPIs &amp; Objectifs RH!N12),0)</t>
-        </is>
-      </c>
-      <c r="Q25" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((P25-O25)/MAX(ABS(O25),0.001),0)</t>
-        </is>
-      </c>
-      <c r="R25" s="73">
-        <f>IF(Q25&gt;=0.1,"✅",IF(Q25&gt;=-0.1,"⚠️","❌"))</f>
+      <c r="P25" s="83">
+        <f>IFERROR(AVERAGE(L12,M12,N12),0)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="85">
+        <f>IFERROR((P25-O25)/MAX(ABS(O25),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="R25" s="86">
+        <f>IF(Q25&gt;=0.1,"OK",IF(Q25&gt;=-0.1,"ATT","NOK"))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="62" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>Nb candidats / embauche</t>
         </is>
       </c>
-      <c r="C26" s="71" t="n">
+      <c r="C26" s="84" t="n">
         <v>15</v>
       </c>
-      <c r="D26" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!C13,19-KPIs &amp; Objectifs RH!D13,19-KPIs &amp; Objectifs RH!E13),0)</t>
-        </is>
-      </c>
-      <c r="E26" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((C26-D26)/MAX(ABS(C26),0.001),0)</t>
-        </is>
-      </c>
-      <c r="F26" s="73">
-        <f>IF(E26&gt;=0.1,"✅",IF(E26&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="G26" s="71" t="n">
+      <c r="D26" s="81">
+        <f>IFERROR(AVERAGE(C13,D13,E13),0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="85">
+        <f>IFERROR((C26-D26)/MAX(ABS(C26),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="86">
+        <f>IF(E26&gt;=0.1,"OK",IF(E26&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="G26" s="84" t="n">
         <v>12</v>
       </c>
-      <c r="H26" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!F13,19-KPIs &amp; Objectifs RH!G13,19-KPIs &amp; Objectifs RH!H13),0)</t>
-        </is>
-      </c>
-      <c r="I26" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((G26-H26)/MAX(ABS(G26),0.001),0)</t>
-        </is>
-      </c>
-      <c r="J26" s="73">
-        <f>IF(I26&gt;=0.1,"✅",IF(I26&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="K26" s="71" t="n">
+      <c r="H26" s="81">
+        <f>IFERROR(AVERAGE(F13,G13,H13),0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="85">
+        <f>IFERROR((G26-H26)/MAX(ABS(G26),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="86">
+        <f>IF(I26&gt;=0.1,"OK",IF(I26&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="K26" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="L26" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!I13,19-KPIs &amp; Objectifs RH!J13,19-KPIs &amp; Objectifs RH!K13),0)</t>
-        </is>
-      </c>
-      <c r="M26" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((K26-L26)/MAX(ABS(K26),0.001),0)</t>
-        </is>
-      </c>
-      <c r="N26" s="73">
-        <f>IF(M26&gt;=0.1,"✅",IF(M26&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="O26" s="71" t="n">
+      <c r="L26" s="81">
+        <f>IFERROR(AVERAGE(I13,J13,K13),0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="85">
+        <f>IFERROR((K26-L26)/MAX(ABS(K26),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="N26" s="86">
+        <f>IF(M26&gt;=0.1,"OK",IF(M26&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="O26" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="P26" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!L13,19-KPIs &amp; Objectifs RH!M13,19-KPIs &amp; Objectifs RH!N13),0)</t>
-        </is>
-      </c>
-      <c r="Q26" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((O26-P26)/MAX(ABS(O26),0.001),0)</t>
-        </is>
-      </c>
-      <c r="R26" s="73">
-        <f>IF(Q26&gt;=0.1,"✅",IF(Q26&gt;=-0.1,"⚠️","❌"))</f>
+      <c r="P26" s="81">
+        <f>IFERROR(AVERAGE(L13,M13,N13),0)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="85">
+        <f>IFERROR((O26-P26)/MAX(ABS(O26),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="R26" s="86">
+        <f>IF(Q26&gt;=0.1,"OK",IF(Q26&gt;=-0.1,"ATT","NOK"))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="62" t="inlineStr">
+      <c r="B27" s="80" t="inlineStr">
         <is>
           <t>Entretiens / embauche</t>
         </is>
       </c>
-      <c r="C27" s="71" t="n">
+      <c r="C27" s="84" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!C14,19-KPIs &amp; Objectifs RH!D14,19-KPIs &amp; Objectifs RH!E14),0)</t>
-        </is>
-      </c>
-      <c r="E27" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((C27-D27)/MAX(ABS(C27),0.001),0)</t>
-        </is>
-      </c>
-      <c r="F27" s="73">
-        <f>IF(E27&gt;=0.1,"✅",IF(E27&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="G27" s="71" t="n">
+      <c r="D27" s="81">
+        <f>IFERROR(AVERAGE(C14,D14,E14),0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="85">
+        <f>IFERROR((C27-D27)/MAX(ABS(C27),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="86">
+        <f>IF(E27&gt;=0.1,"OK",IF(E27&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="G27" s="84" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!F14,19-KPIs &amp; Objectifs RH!G14,19-KPIs &amp; Objectifs RH!H14),0)</t>
-        </is>
-      </c>
-      <c r="I27" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((G27-H27)/MAX(ABS(G27),0.001),0)</t>
-        </is>
-      </c>
-      <c r="J27" s="73">
-        <f>IF(I27&gt;=0.1,"✅",IF(I27&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="K27" s="71" t="n">
+      <c r="H27" s="81">
+        <f>IFERROR(AVERAGE(F14,G14,H14),0)</f>
+        <v/>
+      </c>
+      <c r="I27" s="85">
+        <f>IFERROR((G27-H27)/MAX(ABS(G27),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="J27" s="86">
+        <f>IF(I27&gt;=0.1,"OK",IF(I27&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="K27" s="84" t="n">
         <v>3.5</v>
       </c>
-      <c r="L27" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!I14,19-KPIs &amp; Objectifs RH!J14,19-KPIs &amp; Objectifs RH!K14),0)</t>
-        </is>
-      </c>
-      <c r="M27" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((K27-L27)/MAX(ABS(K27),0.001),0)</t>
-        </is>
-      </c>
-      <c r="N27" s="73">
-        <f>IF(M27&gt;=0.1,"✅",IF(M27&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-      <c r="O27" s="71" t="n">
+      <c r="L27" s="81">
+        <f>IFERROR(AVERAGE(I14,J14,K14),0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="85">
+        <f>IFERROR((K27-L27)/MAX(ABS(K27),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="N27" s="86">
+        <f>IF(M27&gt;=0.1,"OK",IF(M27&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+      <c r="O27" s="84" t="n">
         <v>3</v>
       </c>
-      <c r="P27" s="63" t="inlineStr">
-        <is>
-          <t>IFERROR(AVERAGE(19-KPIs &amp; Objectifs RH!L14,19-KPIs &amp; Objectifs RH!M14,19-KPIs &amp; Objectifs RH!N14),0)</t>
-        </is>
-      </c>
-      <c r="Q27" s="72" t="inlineStr">
-        <is>
-          <t>IFERROR((O27-P27)/MAX(ABS(O27),0.001),0)</t>
-        </is>
-      </c>
-      <c r="R27" s="73">
-        <f>IF(Q27&gt;=0.1,"✅",IF(Q27&gt;=-0.1,"⚠️","❌"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
+      <c r="P27" s="81">
+        <f>IFERROR(AVERAGE(L14,M14,N14),0)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="85">
+        <f>IFERROR((O27-P27)/MAX(ABS(O27),0.001),0)</f>
+        <v/>
+      </c>
+      <c r="R27" s="86">
+        <f>IF(Q27&gt;=0.1,"OK",IF(Q27&gt;=-0.1,"ATT","NOK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
       <c r="B30" s="32" t="inlineStr">
         <is>
           <t>LEGENDE &amp; METHODOLOGIE</t>
@@ -30762,153 +30647,154 @@
       <c r="G30" s="61" t="n"/>
       <c r="H30" s="61" t="n"/>
       <c r="I30" s="61" t="n"/>
+      <c r="J30" s="61" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="76" t="inlineStr">
-        <is>
-          <t>RAG Vert</t>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>OK (Vert)</t>
         </is>
       </c>
       <c r="C31" s="77" t="inlineStr">
         <is>
-          <t>Objectif depasse de plus de 10% (ecart positif &gt;= +10%)</t>
+          <t>Objectif depasse de plus de 10%</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="78" t="inlineStr">
-        <is>
-          <t>RAG Amber</t>
+      <c r="B32" s="89" t="inlineStr">
+        <is>
+          <t>ATT (Amber)</t>
         </is>
       </c>
       <c r="C32" s="77" t="inlineStr">
         <is>
-          <t>Dans une marge de +/- 10% de l'objectif</t>
+          <t>A +/- 10% de l'objectif</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="79" t="inlineStr">
-        <is>
-          <t>RAG Rouge</t>
+      <c r="B33" s="90" t="inlineStr">
+        <is>
+          <t>NOK (Rouge)</t>
         </is>
       </c>
       <c r="C33" s="77" t="inlineStr">
         <is>
-          <t>En dessous de l'objectif de plus de 10% (ecart negatif &lt; -10%)</t>
+          <t>En dessous de plus de 10%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="91" t="inlineStr">
         <is>
           <t>Time-to-Hire</t>
         </is>
       </c>
       <c r="C35" s="77" t="inlineStr">
         <is>
-          <t>Moyenne (Date Pourvue - Date Demande) par mois, depuis feuille 1</t>
+          <t>Moy. (Date Pourvue - Date Demande) par mois, feuille 1</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="91" t="inlineStr">
         <is>
           <t>Cost-per-Hire</t>
         </is>
       </c>
       <c r="C36" s="77" t="inlineStr">
         <is>
-          <t>Somme (Publication + Cabinet + Entretiens + Formation) / Nb embauches, depuis feuille 10 &amp; 2</t>
+          <t>Somme couts / Nb embauches, feuilles 10 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="91" t="inlineStr">
         <is>
           <t>Quality-of-Hire</t>
         </is>
       </c>
       <c r="C37" s="77" t="inlineStr">
         <is>
-          <t>Score moyen Total (/25) des evaluations, depuis feuille 4</t>
+          <t>Score moyen evaluations (/25), feuille 4</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="91" t="inlineStr">
         <is>
           <t>Taux acceptation</t>
         </is>
       </c>
       <c r="C38" s="77" t="inlineStr">
         <is>
-          <t>Pipeline "Accepte" / ("Accepte" + "Refuse") par mois, depuis feuille 18</t>
+          <t>Pipeline Accepte / (Accepte + Refuse), feuille 18</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="91" t="inlineStr">
         <is>
           <t>Taux remplissage</t>
         </is>
       </c>
       <c r="C39" s="77" t="inlineStr">
         <is>
-          <t>Demandes "Pourvue" / Total demandes par mois, depuis feuille 1</t>
+          <t>Demandes Pourvue / Total, feuille 1</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="91" t="inlineStr">
         <is>
           <t>Taux recommandation</t>
         </is>
       </c>
       <c r="C40" s="77" t="inlineStr">
         <is>
-          <t>Evaluations "Embauche recommandee" / Total evalues, depuis feuille 4</t>
+          <t>Embauche recommandee / Total evalues, feuille 4</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="91" t="inlineStr">
         <is>
           <t>Candidats / embauche</t>
         </is>
       </c>
       <c r="C41" s="77" t="inlineStr">
         <is>
-          <t>Nouvelles candidatures / Embauches definitives, depuis feuille 2</t>
+          <t>Candidatures / Embauches def., feuille 2</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="91" t="inlineStr">
         <is>
           <t>Entretiens / embauche</t>
         </is>
       </c>
       <c r="C42" s="77" t="inlineStr">
         <is>
-          <t>Entretiens "Realise" / Embauches definitives, depuis feuille 3 &amp; 2</t>
+          <t>Entretiens Realises / Embauches, feuilles 3 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="92" t="inlineStr">
         <is>
           <t>Objectifs (bleu)</t>
         </is>
       </c>
       <c r="C44" s="77" t="inlineStr">
         <is>
-          <t>Valeurs modifiables — ajustez les cibles selon votre strategie</t>
+          <t>Valeurs modifiables — ajustez selon votre strategie</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="93" t="inlineStr">
         <is>
           <t>Realise (noir)</t>
         </is>
@@ -30920,765 +30806,767 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="21">
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="C45:J45"/>
+    <mergeCell ref="C35:J35"/>
     <mergeCell ref="C18:F18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="C41:J41"/>
+    <mergeCell ref="C31:J31"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="C40:J40"/>
+    <mergeCell ref="B17:R17"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="C39:J39"/>
     <mergeCell ref="G18:J18"/>
-    <mergeCell ref="C39:J39"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="C33:J33"/>
     <mergeCell ref="C32:J32"/>
     <mergeCell ref="C38:J38"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="C45:J45"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="C41:J41"/>
+    <mergeCell ref="B5:O5"/>
     <mergeCell ref="C37:J37"/>
-    <mergeCell ref="C31:J31"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="C40:J40"/>
-    <mergeCell ref="C35:J35"/>
   </mergeCells>
   <conditionalFormatting sqref="E20">
-    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="expression" priority="4" dxfId="16">
+      <formula>E20&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="17">
+      <formula>AND(E20&gt;=-0.1,E20&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="18">
+      <formula>E20&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I20">
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="8" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J20">
+    <cfRule type="expression" priority="10" dxfId="16">
+      <formula>I20&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="17">
+      <formula>AND(I20&gt;=-0.1,I20&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="18">
+      <formula>I20&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20">
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="13" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="14" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N20">
+    <cfRule type="expression" priority="16" dxfId="16">
+      <formula>M20&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="17">
+      <formula>AND(M20&gt;=-0.1,M20&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="18">
+      <formula>M20&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q20">
-    <cfRule type="cellIs" priority="10" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="19" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="20" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="21" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R20">
+    <cfRule type="expression" priority="22" dxfId="16">
+      <formula>Q20&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="23" dxfId="17">
+      <formula>AND(Q20&gt;=-0.1,Q20&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" dxfId="18">
+      <formula>Q20&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="cellIs" priority="13" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="25" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="26" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="27" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="expression" priority="28" dxfId="16">
+      <formula>E21&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" dxfId="17">
+      <formula>AND(E21&gt;=-0.1,E21&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="18">
+      <formula>E21&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" priority="16" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="31" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="17" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="32" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="33" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J21">
+    <cfRule type="expression" priority="34" dxfId="16">
+      <formula>I21&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="17">
+      <formula>AND(I21&gt;=-0.1,I21&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="18">
+      <formula>I21&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21">
-    <cfRule type="cellIs" priority="19" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="37" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="20" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="38" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="21" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="39" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N21">
+    <cfRule type="expression" priority="40" dxfId="16">
+      <formula>M21&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="41" dxfId="17">
+      <formula>AND(M21&gt;=-0.1,M21&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="42" dxfId="18">
+      <formula>M21&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q21">
-    <cfRule type="cellIs" priority="22" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="43" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="23" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="44" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="24" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="45" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R21">
+    <cfRule type="expression" priority="46" dxfId="16">
+      <formula>Q21&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="47" dxfId="17">
+      <formula>AND(Q21&gt;=-0.1,Q21&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="48" dxfId="18">
+      <formula>Q21&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="cellIs" priority="25" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="49" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="26" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="50" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="27" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="51" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="expression" priority="52" dxfId="16">
+      <formula>E22&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="53" dxfId="17">
+      <formula>AND(E22&gt;=-0.1,E22&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="54" dxfId="18">
+      <formula>E22&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="cellIs" priority="28" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="55" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="29" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="56" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="30" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="57" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22">
+    <cfRule type="expression" priority="58" dxfId="16">
+      <formula>I22&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="59" dxfId="17">
+      <formula>AND(I22&gt;=-0.1,I22&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="60" dxfId="18">
+      <formula>I22&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22">
-    <cfRule type="cellIs" priority="31" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="61" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="32" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="62" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="33" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="63" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N22">
+    <cfRule type="expression" priority="64" dxfId="16">
+      <formula>M22&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="65" dxfId="17">
+      <formula>AND(M22&gt;=-0.1,M22&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="66" dxfId="18">
+      <formula>M22&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q22">
-    <cfRule type="cellIs" priority="34" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="67" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="35" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="68" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="36" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="69" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R22">
+    <cfRule type="expression" priority="70" dxfId="16">
+      <formula>Q22&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="71" dxfId="17">
+      <formula>AND(Q22&gt;=-0.1,Q22&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="72" dxfId="18">
+      <formula>Q22&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="cellIs" priority="37" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="73" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="38" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="74" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="39" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="75" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="expression" priority="76" dxfId="16">
+      <formula>E23&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="77" dxfId="17">
+      <formula>AND(E23&gt;=-0.1,E23&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="78" dxfId="18">
+      <formula>E23&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="cellIs" priority="40" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="79" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="41" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="80" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="42" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="81" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23">
+    <cfRule type="expression" priority="82" dxfId="16">
+      <formula>I23&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="83" dxfId="17">
+      <formula>AND(I23&gt;=-0.1,I23&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="84" dxfId="18">
+      <formula>I23&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23">
-    <cfRule type="cellIs" priority="43" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="85" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="44" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="86" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="45" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="87" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N23">
+    <cfRule type="expression" priority="88" dxfId="16">
+      <formula>M23&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="89" dxfId="17">
+      <formula>AND(M23&gt;=-0.1,M23&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="90" dxfId="18">
+      <formula>M23&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q23">
-    <cfRule type="cellIs" priority="46" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="91" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="47" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="92" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="48" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="93" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R23">
+    <cfRule type="expression" priority="94" dxfId="16">
+      <formula>Q23&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="95" dxfId="17">
+      <formula>AND(Q23&gt;=-0.1,Q23&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="96" dxfId="18">
+      <formula>Q23&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" priority="49" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="97" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="50" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="98" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="51" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="99" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
+    <cfRule type="expression" priority="100" dxfId="16">
+      <formula>E24&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="101" dxfId="17">
+      <formula>AND(E24&gt;=-0.1,E24&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="102" dxfId="18">
+      <formula>E24&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24">
-    <cfRule type="cellIs" priority="52" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="103" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="53" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="104" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="54" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="105" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24">
+    <cfRule type="expression" priority="106" dxfId="16">
+      <formula>I24&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="107" dxfId="17">
+      <formula>AND(I24&gt;=-0.1,I24&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="108" dxfId="18">
+      <formula>I24&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24">
-    <cfRule type="cellIs" priority="55" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="109" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="56" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="110" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="57" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="111" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N24">
+    <cfRule type="expression" priority="112" dxfId="16">
+      <formula>M24&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="113" dxfId="17">
+      <formula>AND(M24&gt;=-0.1,M24&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="114" dxfId="18">
+      <formula>M24&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q24">
-    <cfRule type="cellIs" priority="58" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="115" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="59" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="116" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="60" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="117" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R24">
+    <cfRule type="expression" priority="118" dxfId="16">
+      <formula>Q24&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="119" dxfId="17">
+      <formula>AND(Q24&gt;=-0.1,Q24&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="120" dxfId="18">
+      <formula>Q24&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25">
-    <cfRule type="cellIs" priority="61" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="121" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="62" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="122" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="63" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="123" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="expression" priority="124" dxfId="16">
+      <formula>E25&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="125" dxfId="17">
+      <formula>AND(E25&gt;=-0.1,E25&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="126" dxfId="18">
+      <formula>E25&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25">
-    <cfRule type="cellIs" priority="64" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="127" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="65" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="128" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="66" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="129" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25">
+    <cfRule type="expression" priority="130" dxfId="16">
+      <formula>I25&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="131" dxfId="17">
+      <formula>AND(I25&gt;=-0.1,I25&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="132" dxfId="18">
+      <formula>I25&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25">
-    <cfRule type="cellIs" priority="67" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="133" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="68" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="134" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="69" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="135" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N25">
+    <cfRule type="expression" priority="136" dxfId="16">
+      <formula>M25&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="137" dxfId="17">
+      <formula>AND(M25&gt;=-0.1,M25&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="138" dxfId="18">
+      <formula>M25&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q25">
-    <cfRule type="cellIs" priority="70" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="139" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="71" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="140" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="72" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="141" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R25">
+    <cfRule type="expression" priority="142" dxfId="16">
+      <formula>Q25&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="143" dxfId="17">
+      <formula>AND(Q25&gt;=-0.1,Q25&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="144" dxfId="18">
+      <formula>Q25&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26">
-    <cfRule type="cellIs" priority="73" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="145" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="74" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="146" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="75" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="147" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="expression" priority="148" dxfId="16">
+      <formula>E26&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="149" dxfId="17">
+      <formula>AND(E26&gt;=-0.1,E26&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="150" dxfId="18">
+      <formula>E26&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26">
-    <cfRule type="cellIs" priority="76" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="151" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="77" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="152" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="78" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="153" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J26">
+    <cfRule type="expression" priority="154" dxfId="16">
+      <formula>I26&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="155" dxfId="17">
+      <formula>AND(I26&gt;=-0.1,I26&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="156" dxfId="18">
+      <formula>I26&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26">
-    <cfRule type="cellIs" priority="79" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="157" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="80" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="158" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="81" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="159" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N26">
+    <cfRule type="expression" priority="160" dxfId="16">
+      <formula>M26&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="161" dxfId="17">
+      <formula>AND(M26&gt;=-0.1,M26&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="162" dxfId="18">
+      <formula>M26&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q26">
-    <cfRule type="cellIs" priority="82" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="163" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="83" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="164" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="84" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="165" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R26">
+    <cfRule type="expression" priority="166" dxfId="16">
+      <formula>Q26&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="167" dxfId="17">
+      <formula>AND(Q26&gt;=-0.1,Q26&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="168" dxfId="18">
+      <formula>Q26&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27">
-    <cfRule type="cellIs" priority="85" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="169" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="86" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="170" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="87" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="171" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="expression" priority="172" dxfId="16">
+      <formula>E27&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="173" dxfId="17">
+      <formula>AND(E27&gt;=-0.1,E27&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="174" dxfId="18">
+      <formula>E27&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27">
-    <cfRule type="cellIs" priority="88" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="175" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="89" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="176" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="90" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="177" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27">
+    <cfRule type="expression" priority="178" dxfId="16">
+      <formula>I27&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="179" dxfId="17">
+      <formula>AND(I27&gt;=-0.1,I27&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="180" dxfId="18">
+      <formula>I27&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M27">
-    <cfRule type="cellIs" priority="91" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="181" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="92" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="182" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="93" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="183" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N27">
+    <cfRule type="expression" priority="184" dxfId="16">
+      <formula>M27&gt;=0.1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="185" dxfId="17">
+      <formula>AND(M27&gt;=-0.1,M27&lt;0.1)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="186" dxfId="18">
+      <formula>M27&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q27">
-    <cfRule type="cellIs" priority="94" operator="greaterThanOrEqual" dxfId="10">
+    <cfRule type="cellIs" priority="187" operator="greaterThanOrEqual" dxfId="16">
       <formula>0.1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="95" operator="between" dxfId="11">
+    <cfRule type="cellIs" priority="188" operator="between" dxfId="17">
       <formula>-0.1</formula>
       <formula>0.0999</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="96" operator="lessThan" dxfId="12">
+    <cfRule type="cellIs" priority="189" operator="lessThan" dxfId="18">
       <formula>-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="expression" priority="97" dxfId="13">
-      <formula>E20&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="98" dxfId="14">
-      <formula>AND(E20&gt;=-0.1,E20&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="99" dxfId="15">
-      <formula>E20&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J20">
-    <cfRule type="expression" priority="100" dxfId="13">
-      <formula>I20&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="101" dxfId="14">
-      <formula>AND(I20&gt;=-0.1,I20&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="102" dxfId="15">
-      <formula>I20&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N20">
-    <cfRule type="expression" priority="103" dxfId="13">
-      <formula>M20&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="104" dxfId="14">
-      <formula>AND(M20&gt;=-0.1,M20&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="105" dxfId="15">
-      <formula>M20&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R20">
-    <cfRule type="expression" priority="106" dxfId="13">
-      <formula>Q20&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="107" dxfId="14">
-      <formula>AND(Q20&gt;=-0.1,Q20&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="108" dxfId="15">
-      <formula>Q20&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="expression" priority="109" dxfId="13">
-      <formula>E21&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="110" dxfId="14">
-      <formula>AND(E21&gt;=-0.1,E21&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="111" dxfId="15">
-      <formula>E21&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J21">
-    <cfRule type="expression" priority="112" dxfId="13">
-      <formula>I21&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="113" dxfId="14">
-      <formula>AND(I21&gt;=-0.1,I21&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="114" dxfId="15">
-      <formula>I21&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N21">
-    <cfRule type="expression" priority="115" dxfId="13">
-      <formula>M21&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="116" dxfId="14">
-      <formula>AND(M21&gt;=-0.1,M21&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="117" dxfId="15">
-      <formula>M21&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R21">
-    <cfRule type="expression" priority="118" dxfId="13">
-      <formula>Q21&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="119" dxfId="14">
-      <formula>AND(Q21&gt;=-0.1,Q21&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="120" dxfId="15">
-      <formula>Q21&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="expression" priority="121" dxfId="13">
-      <formula>E22&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="122" dxfId="14">
-      <formula>AND(E22&gt;=-0.1,E22&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="123" dxfId="15">
-      <formula>E22&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J22">
-    <cfRule type="expression" priority="124" dxfId="13">
-      <formula>I22&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="125" dxfId="14">
-      <formula>AND(I22&gt;=-0.1,I22&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="126" dxfId="15">
-      <formula>I22&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22">
-    <cfRule type="expression" priority="127" dxfId="13">
-      <formula>M22&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="128" dxfId="14">
-      <formula>AND(M22&gt;=-0.1,M22&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="129" dxfId="15">
-      <formula>M22&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R22">
-    <cfRule type="expression" priority="130" dxfId="13">
-      <formula>Q22&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="131" dxfId="14">
-      <formula>AND(Q22&gt;=-0.1,Q22&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="132" dxfId="15">
-      <formula>Q22&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="expression" priority="133" dxfId="13">
-      <formula>E23&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="134" dxfId="14">
-      <formula>AND(E23&gt;=-0.1,E23&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="135" dxfId="15">
-      <formula>E23&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J23">
-    <cfRule type="expression" priority="136" dxfId="13">
-      <formula>I23&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="137" dxfId="14">
-      <formula>AND(I23&gt;=-0.1,I23&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="138" dxfId="15">
-      <formula>I23&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N23">
-    <cfRule type="expression" priority="139" dxfId="13">
-      <formula>M23&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="140" dxfId="14">
-      <formula>AND(M23&gt;=-0.1,M23&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="141" dxfId="15">
-      <formula>M23&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R23">
-    <cfRule type="expression" priority="142" dxfId="13">
-      <formula>Q23&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="143" dxfId="14">
-      <formula>AND(Q23&gt;=-0.1,Q23&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="144" dxfId="15">
-      <formula>Q23&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24">
-    <cfRule type="expression" priority="145" dxfId="13">
-      <formula>E24&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="146" dxfId="14">
-      <formula>AND(E24&gt;=-0.1,E24&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="147" dxfId="15">
-      <formula>E24&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J24">
-    <cfRule type="expression" priority="148" dxfId="13">
-      <formula>I24&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="149" dxfId="14">
-      <formula>AND(I24&gt;=-0.1,I24&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="150" dxfId="15">
-      <formula>I24&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N24">
-    <cfRule type="expression" priority="151" dxfId="13">
-      <formula>M24&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="152" dxfId="14">
-      <formula>AND(M24&gt;=-0.1,M24&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="153" dxfId="15">
-      <formula>M24&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R24">
-    <cfRule type="expression" priority="154" dxfId="13">
-      <formula>Q24&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="155" dxfId="14">
-      <formula>AND(Q24&gt;=-0.1,Q24&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="156" dxfId="15">
-      <formula>Q24&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="expression" priority="157" dxfId="13">
-      <formula>E25&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="158" dxfId="14">
-      <formula>AND(E25&gt;=-0.1,E25&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="159" dxfId="15">
-      <formula>E25&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
-    <cfRule type="expression" priority="160" dxfId="13">
-      <formula>I25&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="161" dxfId="14">
-      <formula>AND(I25&gt;=-0.1,I25&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="162" dxfId="15">
-      <formula>I25&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N25">
-    <cfRule type="expression" priority="163" dxfId="13">
-      <formula>M25&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="164" dxfId="14">
-      <formula>AND(M25&gt;=-0.1,M25&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="165" dxfId="15">
-      <formula>M25&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R25">
-    <cfRule type="expression" priority="166" dxfId="13">
-      <formula>Q25&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="167" dxfId="14">
-      <formula>AND(Q25&gt;=-0.1,Q25&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="168" dxfId="15">
-      <formula>Q25&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="expression" priority="169" dxfId="13">
-      <formula>E26&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="170" dxfId="14">
-      <formula>AND(E26&gt;=-0.1,E26&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="171" dxfId="15">
-      <formula>E26&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J26">
-    <cfRule type="expression" priority="172" dxfId="13">
-      <formula>I26&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="173" dxfId="14">
-      <formula>AND(I26&gt;=-0.1,I26&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="174" dxfId="15">
-      <formula>I26&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N26">
-    <cfRule type="expression" priority="175" dxfId="13">
-      <formula>M26&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="176" dxfId="14">
-      <formula>AND(M26&gt;=-0.1,M26&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="177" dxfId="15">
-      <formula>M26&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R26">
-    <cfRule type="expression" priority="178" dxfId="13">
-      <formula>Q26&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="179" dxfId="14">
-      <formula>AND(Q26&gt;=-0.1,Q26&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="180" dxfId="15">
-      <formula>Q26&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="expression" priority="181" dxfId="13">
-      <formula>E27&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="182" dxfId="14">
-      <formula>AND(E27&gt;=-0.1,E27&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="183" dxfId="15">
-      <formula>E27&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
-    <cfRule type="expression" priority="184" dxfId="13">
-      <formula>I27&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="185" dxfId="14">
-      <formula>AND(I27&gt;=-0.1,I27&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="186" dxfId="15">
-      <formula>I27&lt;-0.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N27">
-    <cfRule type="expression" priority="187" dxfId="13">
-      <formula>M27&gt;=0.1</formula>
-    </cfRule>
-    <cfRule type="expression" priority="188" dxfId="14">
-      <formula>AND(M27&gt;=-0.1,M27&lt;0.1)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="189" dxfId="15">
-      <formula>M27&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R27">
-    <cfRule type="expression" priority="190" dxfId="13">
+    <cfRule type="expression" priority="190" dxfId="16">
       <formula>Q27&gt;=0.1</formula>
     </cfRule>
-    <cfRule type="expression" priority="191" dxfId="14">
+    <cfRule type="expression" priority="191" dxfId="17">
       <formula>AND(Q27&gt;=-0.1,Q27&lt;0.1)</formula>
     </cfRule>
-    <cfRule type="expression" priority="192" dxfId="15">
+    <cfRule type="expression" priority="192" dxfId="18">
       <formula>Q27&lt;-0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
